--- a/Result/profitability/2812.xlsx
+++ b/Result/profitability/2812.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,7 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.37625</v>
+        <v>0.38875</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -750,7 +750,7 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34875</v>
+        <v>0.36375</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -849,7 +849,7 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.30875</v>
+        <v>0.31875</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -948,7 +948,7 @@
         <v>-0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.21875</v>
+        <v>0.23125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1047,7 +1047,7 @@
         <v>-0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16625</v>
+        <v>0.1725</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1150,7 +1150,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02750000000000001</v>
+        <v>0.03625</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1253,7 +1253,7 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.004999999999999991</v>
+        <v>0.003750000000000003</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -8114,6 +8114,109 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6331</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>3357</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2843</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1749999999999998</v>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2702702702702702</v>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
